--- a/scheduling_recent.xlsx
+++ b/scheduling_recent.xlsx
@@ -11008,7 +11008,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11094,6 +11094,72 @@
         </is>
       </c>
       <c r="D4" t="inlineStr">
+        <is>
+          <t>User logged in</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-02-11 19:36:27</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>admin@example.com</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Login</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>User logged in</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-02-11 19:38:59</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>admin@example.com</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Login</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>User logged in</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-02-11 19:39:49</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>admin@example.com</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Login</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
         <is>
           <t>User logged in</t>
         </is>

--- a/scheduling_recent.xlsx
+++ b/scheduling_recent.xlsx
@@ -11008,7 +11008,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:D8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11160,6 +11160,28 @@
         </is>
       </c>
       <c r="D7" t="inlineStr">
+        <is>
+          <t>User logged in</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-02-11 19:45:44</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>admin@example.com</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Login</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
         <is>
           <t>User logged in</t>
         </is>

--- a/scheduling_recent.xlsx
+++ b/scheduling_recent.xlsx
@@ -11008,7 +11008,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11182,6 +11182,28 @@
         </is>
       </c>
       <c r="D8" t="inlineStr">
+        <is>
+          <t>User logged in</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-02-11 19:49:23</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>admin@example.com</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Login</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
         <is>
           <t>User logged in</t>
         </is>

--- a/scheduling_recent.xlsx
+++ b/scheduling_recent.xlsx
@@ -11008,7 +11008,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11204,6 +11204,28 @@
         </is>
       </c>
       <c r="D9" t="inlineStr">
+        <is>
+          <t>User logged in</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-02-11 22:48:12</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>admin@example.com</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Login</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
         <is>
           <t>User logged in</t>
         </is>
